--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:27</t>
+    <t xml:space="preserve">2026-09-10 01:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:41</t>
+    <t xml:space="preserve">2026-09-18 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:37</t>
+    <t xml:space="preserve">2026-09-23 15:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:43</t>
+    <t xml:space="preserve">2026-10-05 16:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -732,7 +732,7 @@
         <v>60.96</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>97.62</v>
+        <v>97.63</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>90.53</v>
@@ -895,7 +895,7 @@
         <v>108.27</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>60.62</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="13">
